--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104534_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104534_W9.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3456</v>
+        <v>8.318899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4903</v>
+        <v>6.2466</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8553</v>
+        <v>2.0723</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3594</v>
+        <v>7.3495</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5064</v>
+        <v>0.5083</v>
       </c>
       <c r="I2" t="n">
-        <v>6.853</v>
+        <v>6.8413</v>
       </c>
       <c r="J2" t="n">
-        <v>7.1347</v>
+        <v>7.1015</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4604</v>
+        <v>0.4514</v>
       </c>
       <c r="L2" t="n">
-        <v>6.6743</v>
+        <v>6.6501</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2247</v>
+        <v>0.2481</v>
       </c>
       <c r="N2" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0194</v>
+        <v>1.0083</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4688</v>
+        <v>0.3319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4881</v>
+        <v>0.6763</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8741</v>
+        <v>0.8716</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2185</v>
+        <v>-0.2179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4406</v>
+        <v>6.402</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4655</v>
+        <v>4.0749</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9751</v>
+        <v>2.3271</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4328</v>
+        <v>4.0044</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4358</v>
+        <v>0.9164</v>
       </c>
       <c r="I3" t="n">
-        <v>0.997</v>
+        <v>3.088</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1077</v>
+        <v>3.1102</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9958</v>
+        <v>0.2133</v>
       </c>
       <c r="L3" t="n">
-        <v>0.112</v>
+        <v>2.8968</v>
       </c>
       <c r="M3" t="n">
-        <v>1.325</v>
+        <v>0.8942</v>
       </c>
       <c r="N3" t="n">
-        <v>0.44</v>
+        <v>0.703</v>
       </c>
       <c r="O3" t="n">
-        <v>0.885</v>
+        <v>0.1912</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4596</v>
+        <v>1.1814</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9436</v>
+        <v>0.2622</v>
       </c>
       <c r="U3" t="n">
-        <v>0.516</v>
+        <v>0.9192</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3214</v>
+        <v>-0.6049</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4141</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.3074</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0732</v>
+        <v>5.8928</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3745</v>
+        <v>5.0909</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6987</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0059</v>
+        <v>4.4297</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9192</v>
+        <v>3.4269</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0867</v>
+        <v>1.0028</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1362</v>
+        <v>3.0937</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2282</v>
+        <v>2.982</v>
       </c>
       <c r="L4" t="n">
-        <v>2.908</v>
+        <v>0.1117</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8697</v>
+        <v>1.336</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.4449</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1787</v>
+        <v>0.8911</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8568</v>
+        <v>0.92</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4688</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3256</v>
+        <v>0.3278</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6041</v>
+        <v>0.3155</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>1.405</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3112</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5466</v>
+        <v>4.794</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5253</v>
+        <v>2.7561</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0214</v>
+        <v>2.0379</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2861</v>
+        <v>3.1483</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2092</v>
+        <v>1.3417</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0769</v>
+        <v>1.8066</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1282</v>
+        <v>2.7147</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9741</v>
+        <v>1.4716</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1541</v>
+        <v>1.243</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1578</v>
+        <v>0.4336</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2351</v>
+        <v>-0.13</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>0.5636</v>
       </c>
       <c r="P5" t="n">
+        <v>2.0487</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.1342</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2606</v>
+        <v>-0.403</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4386</v>
+        <v>0.0414</v>
       </c>
       <c r="U5" t="n">
-        <v>0.822</v>
+        <v>-0.4444</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4505</v>
+        <v>4.0842</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7228</v>
+        <v>3.2882</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7277</v>
+        <v>0.796</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1618</v>
+        <v>3.2872</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3493</v>
+        <v>2.2087</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8125</v>
+        <v>1.0786</v>
       </c>
       <c r="J6" t="n">
-        <v>2.753</v>
+        <v>3.1117</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4923</v>
+        <v>1.965</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2607</v>
+        <v>1.1467</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4088</v>
+        <v>0.1755</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1431</v>
+        <v>0.2437</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0415</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7528</v>
+        <v>0.797</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0302</v>
+        <v>0.2252</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7226</v>
+        <v>0.5718</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0722</v>
+        <v>1.3925</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9484</v>
+        <v>2.4203</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8762</v>
+        <v>-1.0279</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8312</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0031</v>
+        <v>0.0107</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8343</v>
+        <v>0.8295</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9687</v>
+        <v>0.9513</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8129</v>
+        <v>0.7962</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1375</v>
+        <v>-0.1111</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5819</v>
+        <v>-0.2786</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6593</v>
+        <v>-0.1652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0774</v>
+        <v>-0.1133</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7649</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4039</v>
+        <v>-2.3968</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.1181</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0995</v>
+        <v>-0.9852</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0368</v>
+        <v>1.1033</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5064</v>
+        <v>0.5083</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3492</v>
+        <v>0.3503</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1155</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6951</v>
+        <v>-1.2941</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9067</v>
+        <v>-4.7023</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2116</v>
+        <v>3.4083</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8151</v>
+        <v>2.8164</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4978</v>
+        <v>-1.4991</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3128</v>
+        <v>4.3155</v>
       </c>
       <c r="J9" t="n">
-        <v>1.364</v>
+        <v>1.3338</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1411</v>
+        <v>-2.1588</v>
       </c>
       <c r="L9" t="n">
-        <v>3.5051</v>
+        <v>3.4926</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4511</v>
+        <v>1.4826</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8078</v>
+        <v>0.8229</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.3098</v>
+        <v>-4.325</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3675</v>
+        <v>0.0455</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0121</v>
+        <v>0.2481</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3554</v>
+        <v>-0.2026</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1671</v>
+        <v>0.1691</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3793</v>
+        <v>-0.3757</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7851</v>
+        <v>-2.0271</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1843</v>
+        <v>-0.4628</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6009</v>
+        <v>-1.5643</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2777</v>
+        <v>0.7138</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6264</v>
+        <v>-0.9709</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3487</v>
+        <v>1.6846</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3774</v>
+        <v>1.8161</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9426</v>
+        <v>-0.4104</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5652</v>
+        <v>2.2265</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0998</v>
+        <v>-1.1023</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3162</v>
+        <v>-0.5604</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7835</v>
+        <v>-0.5419</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2465</v>
+        <v>0.1696</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4779</v>
+        <v>-0.1604</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2314</v>
+        <v>0.33</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0824</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3112</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4612</v>
+        <v>-2.1994</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-1.7931</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8367</v>
+        <v>-0.4063</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7147</v>
+        <v>0.2756</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9726</v>
+        <v>1.6175</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6873</v>
+        <v>-1.3418</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8309</v>
+        <v>1.3459</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4054</v>
+        <v>1.9198</v>
       </c>
       <c r="L11" t="n">
-        <v>2.2363</v>
+        <v>-0.5739</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1162</v>
+        <v>-1.0703</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5672</v>
+        <v>-0.3023</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.549</v>
+        <v>-0.768</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2686</v>
+        <v>-0.1661</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>-0.0887</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0774</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-2.0813</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>-0.7739</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2534</v>
+        <v>-1.3074</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5634</v>
+        <v>-4.0838</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5696</v>
+        <v>-1.0583</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9938</v>
+        <v>-3.0255</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3012</v>
+        <v>0.3063</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2048</v>
+        <v>1.2089</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9036</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3165</v>
+        <v>0.3031</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1429</v>
+        <v>1.1376</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0153</v>
+        <v>0.0032</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.199</v>
+        <v>-0.7363</v>
       </c>
       <c r="T12" t="n">
-        <v>0.248</v>
+        <v>-0.2232</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.447</v>
+        <v>-0.513</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.3611</v>
+        <v>21.3981</v>
       </c>
       <c r="E13" t="n">
-        <v>14.1422</v>
+        <v>14.8753</v>
       </c>
       <c r="F13" t="n">
-        <v>6.219000000000001</v>
+        <v>6.522800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>27.69230000000001</v>
+        <v>27.6797</v>
       </c>
       <c r="H13" t="n">
-        <v>9.126799999999999</v>
+        <v>9.119399999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>18.5655</v>
+        <v>18.5603</v>
       </c>
       <c r="J13" t="n">
-        <v>25.1519</v>
+        <v>24.9165</v>
       </c>
       <c r="K13" t="n">
-        <v>7.880300000000001</v>
+        <v>7.7611</v>
       </c>
       <c r="L13" t="n">
-        <v>17.2718</v>
+        <v>17.1552</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5401</v>
+        <v>2.763300000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>1.2463</v>
+        <v>1.3582</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2939</v>
+        <v>1.4051</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7442</v>
+        <v>14.7961</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5576</v>
+        <v>2.6029</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1211</v>
+        <v>1.1819</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4364</v>
+        <v>1.421</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.6202</v>
+        <v>-6.6083</v>
       </c>
       <c r="W13" t="n">
-        <v>5.881399999999999</v>
+        <v>5.849299999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.5016</v>
+        <v>-12.4576</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.235</v>
+        <v>5.2256</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8971</v>
+        <v>3.8796</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3379</v>
+        <v>1.346</v>
       </c>
       <c r="G14" t="n">
-        <v>3.796</v>
+        <v>3.789</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7431</v>
+        <v>2.7374</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0529</v>
+        <v>1.0516</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3987</v>
+        <v>3.3862</v>
       </c>
       <c r="K14" t="n">
-        <v>2.13</v>
+        <v>2.1201</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3973</v>
+        <v>0.4028</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6132</v>
+        <v>0.6173</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0514</v>
+        <v>0.0512</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2601</v>
+        <v>0.2603</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8672</v>
+        <v>2.9032</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0714</v>
+        <v>3.1579</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2042</v>
+        <v>-0.2547</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.582</v>
+        <v>-0.5777</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0275</v>
+        <v>-0.0205</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5545</v>
+        <v>-0.5572</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3518</v>
+        <v>1.3255</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7009</v>
+        <v>0.6845</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9338</v>
+        <v>-1.9032</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4243</v>
+        <v>0.4517</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2389</v>
+        <v>-0.1189</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6632</v>
+        <v>0.5707</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5047</v>
+        <v>0.9175</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7428</v>
+        <v>0.4639</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2381</v>
+        <v>0.4536</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1434</v>
+        <v>-1.1559</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2237</v>
+        <v>-0.2213</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9197</v>
+        <v>-0.9347</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4123</v>
+        <v>0.3737</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8074</v>
+        <v>0.7809</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5557</v>
+        <v>-1.5296</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0407</v>
+        <v>-0.6192</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3085</v>
+        <v>-0.544</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7322</v>
+        <v>-0.0752</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8741</v>
+        <v>0.8716</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2185</v>
+        <v>-0.2179</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5784</v>
+        <v>-0.1087</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6286</v>
+        <v>-1.3976</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0502</v>
+        <v>1.2889</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0604</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6175</v>
+        <v>0.6257</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2012</v>
+        <v>0.2007</v>
       </c>
       <c r="K17" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1408</v>
+        <v>-0.1259</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8656</v>
+        <v>-0.4112</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.17</v>
+        <v>0.049</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2611</v>
+        <v>-1.2836</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4602</v>
+        <v>0.1774</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7214</v>
+        <v>-1.461</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.7062</v>
+        <v>-4.7149</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6809</v>
+        <v>-1.6911</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.0254</v>
+        <v>-3.0239</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3702</v>
+        <v>-1.4076</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8769</v>
+        <v>-0.9005</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.3361</v>
+        <v>-3.3073</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5321</v>
+        <v>-2.5168</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4637</v>
+        <v>0.4493</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4597</v>
+        <v>0.2271</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0039</v>
+        <v>0.2221</v>
       </c>
       <c r="V18" t="n">
-        <v>2.301</v>
+        <v>2.2992</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4307</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1552</v>
+        <v>-3.1066</v>
       </c>
       <c r="E19" t="n">
-        <v>0.879</v>
+        <v>-0.1968</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0342</v>
+        <v>-2.9098</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9409</v>
+        <v>-2.9326</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9148</v>
+        <v>-1.9156</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0262</v>
+        <v>-1.017</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5765</v>
+        <v>0.5631</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5175</v>
+        <v>-3.4957</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2576</v>
+        <v>-2.2458</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8289</v>
+        <v>0.8651</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6635</v>
+        <v>0.6059</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1654</v>
+        <v>0.2592</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8163</v>
+        <v>-0.8114</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8163</v>
+        <v>-0.8114</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0242</v>
+        <v>-3.2685</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0397</v>
+        <v>-1.714</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9845</v>
+        <v>-1.5546</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1063</v>
+        <v>-2.1038</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.3404</v>
+        <v>-3.3402</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2342</v>
+        <v>1.2365</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2489</v>
+        <v>0.2328</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.0647</v>
+        <v>-2.0759</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3136</v>
+        <v>2.3087</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3552</v>
+        <v>-2.3365</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7672</v>
+        <v>-1.0072</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8861</v>
+        <v>-0.5323</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.881</v>
+        <v>-0.4749</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1881</v>
+        <v>-3.8861</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4731</v>
+        <v>-2.2147</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7149</v>
+        <v>-1.6714</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.5586</v>
+        <v>-3.2545</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6002</v>
+        <v>-2.0796</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.9584</v>
+        <v>-1.1749</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1448</v>
+        <v>-0.5745</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4818</v>
+        <v>-0.6862</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.663</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4139</v>
+        <v>-2.68</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1185</v>
+        <v>-1.3934</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1603</v>
+        <v>-0.1372</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6866</v>
+        <v>-0.2744</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5263</v>
+        <v>0.1372</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9834000000000001</v>
+        <v>-0.2667</v>
       </c>
       <c r="W21" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3627</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3428</v>
+        <v>-4.7114</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6785</v>
+        <v>-2.3421</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6643</v>
+        <v>-2.3693</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2671</v>
+        <v>-5.5686</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0837</v>
+        <v>-1.5998</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1834</v>
+        <v>-3.9688</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5705</v>
+        <v>-3.1755</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6825</v>
+        <v>-0.4934</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>-2.6822</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6966</v>
+        <v>-2.3931</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4012</v>
+        <v>-1.1064</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5789</v>
+        <v>-0.351</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.747</v>
+        <v>-0.1375</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1681</v>
+        <v>-0.2135</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.27</v>
+        <v>0.9805</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.27</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1683</v>
+        <v>-5.4621</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6139</v>
+        <v>-3.0482</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5545</v>
+        <v>-2.4139</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.679</v>
+        <v>-3.5589</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3248</v>
+        <v>-1.2951</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.3542</v>
+        <v>-2.2638</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1516</v>
+        <v>-0.5093</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4546</v>
+        <v>-0.3899</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.6062</v>
+        <v>-0.1194</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.5274</v>
+        <v>-3.0496</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7794</v>
+        <v>-0.9052</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.748</v>
+        <v>-2.1444</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5878</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-4.7803</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0321</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3962</v>
+        <v>0.0624</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4282</v>
+        <v>0.4683</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1093</v>
+        <v>0.9805</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.27</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2499</v>
+        <v>-5.9924</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8358</v>
+        <v>-3.2881</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4141</v>
+        <v>-2.7043</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.565</v>
+        <v>-7.6765</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2914</v>
+        <v>-0.3191</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2736</v>
+        <v>-7.3574</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4925</v>
+        <v>-3.1782</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3779</v>
+        <v>1.4479</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1147</v>
+        <v>-4.6261</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.0725</v>
+        <v>-4.4982</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9135</v>
+        <v>-1.767</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.159</v>
+        <v>-2.7312</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4025</v>
+        <v>1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7635</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2659</v>
+        <v>0.1996</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7652</v>
+        <v>-0.04</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4993</v>
+        <v>0.2396</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9834000000000001</v>
+        <v>-0.1089</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2019</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.3611</v>
+        <v>-18.7731</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.219099999999999</v>
+        <v>-6.5227</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.1421</v>
+        <v>-12.2505</v>
       </c>
       <c r="G25" t="n">
-        <v>-27.6921</v>
+        <v>-27.6796</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.126799999999999</v>
+        <v>-9.119200000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-18.5653</v>
+        <v>-18.5605</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.540200000000001</v>
+        <v>-2.7631</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.246400000000001</v>
+        <v>-1.3581</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2936</v>
+        <v>-1.4052</v>
       </c>
       <c r="M25" t="n">
-        <v>-25.1522</v>
+        <v>-24.9163</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.8805</v>
+        <v>-7.761099999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-17.2718</v>
+        <v>-17.155</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.7442</v>
+        <v>-14.7961</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5576</v>
+        <v>0.02179999999999993</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4364</v>
+        <v>-1.4209</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1212999999999999</v>
+        <v>1.4428</v>
       </c>
       <c r="V25" t="n">
-        <v>6.620200000000001</v>
+        <v>6.6083</v>
       </c>
       <c r="W25" t="n">
-        <v>12.5016</v>
+        <v>12.4575</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.8813</v>
+        <v>-5.8491</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104534_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104534_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2179</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.3074</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.3968</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3757</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.3074</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-12.4576</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.2179</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.8114</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104534_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-5.8491</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
